--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaibi</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Doan</t>
+          <t>E. Fernandez</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E. Fernandez</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1407,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">

--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabelle'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorie-Profil'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,22 +476,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>38.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.5</v>
+        <v>37.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -548,22 +548,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Fischköppe</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fischköppe</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.5</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -626,13 +626,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,29 +650,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ST 3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>kum. ST 3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="C2" t="n">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="n">
-        <v>23.5</v>
+        <v>39</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -683,58 +701,82 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E3" t="n">
         <v>20</v>
       </c>
-      <c r="D3" t="n">
-        <v>20</v>
+      <c r="F3" t="n">
+        <v>38.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="C4" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>18.5</v>
+        <v>37.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="C5" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="n">
-        <v>17.5</v>
+        <v>36</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="D6" t="n">
-        <v>13.5</v>
+        <v>33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -747,14 +789,20 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E7" t="n">
         <v>12</v>
       </c>
-      <c r="D7" t="n">
-        <v>12</v>
+      <c r="F7" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -817,26 +865,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>23.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -846,97 +894,97 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>18.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>13.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -946,22 +994,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1089,7 +1137,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1098,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1113,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1179,7 +1227,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Upamecano</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1202,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1217,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1231,30 +1279,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Upamecano</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1269,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1283,12 +1331,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Doan</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1297,16 +1345,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1335,12 +1383,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E. Fernandez</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1349,7 +1397,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1358,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1376,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1387,12 +1435,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>E. Fernandez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1401,22 +1449,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1428,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1439,12 +1487,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kimmich</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1459,10 +1507,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1491,21 +1539,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gregoritsch</t>
+          <t>Kimmich</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1514,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1543,17 +1591,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Mohya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1563,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1595,17 +1643,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Backhaus</t>
+          <t>Gregoritsch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1618,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1642,26 +1690,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1670,46 +1718,46 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mittelstädt</t>
+          <t>Matanovic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1722,50 +1770,50 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vagnoman</t>
+          <t>Backhaus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1774,22 +1822,22 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1803,30 +1851,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>Lukeba</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1855,21 +1903,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karetsas</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1878,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,16 +1935,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1907,7 +1955,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stiller</t>
+          <t>Mittelstädt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1917,11 +1965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1930,22 +1978,22 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
         <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1959,17 +2007,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>Vagnoman</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1982,22 +2030,22 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2011,12 +2059,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wimmer</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2025,22 +2073,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2052,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2063,7 +2111,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guirassy</t>
+          <t>Karetsas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2073,7 +2121,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2086,19 +2134,19 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2115,17 +2163,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pejcinovic</t>
+          <t>S. El Mala</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2135,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2167,21 +2215,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flekken</t>
+          <t>Stiller</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2214,35 +2262,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2251,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2266,26 +2314,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeltsch</t>
+          <t>Wimmer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2294,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2303,13 +2351,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2318,26 +2366,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lienhart</t>
+          <t>Guirassy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2346,19 +2394,19 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2370,26 +2418,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Pejcinovic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2398,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2422,22 +2470,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Flekken</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2474,22 +2522,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grönbaek</t>
+          <t>Zentner</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2502,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2517,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2531,17 +2579,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2554,22 +2602,22 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2583,21 +2631,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Onyeka</t>
+          <t>Jeltsch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2606,22 +2654,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
         <v>3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2635,21 +2683,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lemperle</t>
+          <t>Lienhart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2658,13 +2706,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2687,17 +2735,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Olise</t>
+          <t>Simpson-Pusey</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2710,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2725,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2739,21 +2787,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kobel</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2762,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2777,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2786,26 +2834,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Laimer</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2814,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2838,26 +2886,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ryerson</t>
+          <t>Grönbaek</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2866,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2881,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2890,26 +2938,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tapsoba</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2918,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2942,17 +2990,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Leweling</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2967,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2994,17 +3042,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>El Khannouss</t>
+          <t>Onyeka</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3022,13 +3070,13 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3046,22 +3094,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>Lemperle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3074,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3092,28 +3140,28 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pavlovic</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3126,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3150,26 +3198,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Uzun</t>
+          <t>Olise</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3178,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3202,26 +3250,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Burkardt</t>
+          <t>Kobel</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3230,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>4</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3259,17 +3307,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Demirovic</t>
+          <t>Laimer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3279,16 +3327,16 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3311,17 +3359,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neuer</t>
+          <t>Raum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3358,12 +3406,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Ryerson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3377,7 +3425,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3386,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3395,10 +3443,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -3410,12 +3458,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Tapsoba</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3429,7 +3477,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -3438,36 +3486,36 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quansah</t>
+          <t>Aleix Garcia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3477,7 +3525,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3490,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3499,32 +3547,32 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Avdullahu</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3542,13 +3590,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3566,12 +3614,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Führich</t>
+          <t>El Khannouss</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3594,13 +3642,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3618,17 +3666,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M. Eggestein</t>
+          <t>Gruda</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3646,13 +3694,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3670,17 +3718,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Petkov</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3689,7 +3737,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3698,41 +3746,41 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Prömel</t>
+          <t>Pavlovic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3741,7 +3789,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3750,19 +3798,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3774,12 +3822,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ebnoutalib</t>
+          <t>Uzun</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3789,11 +3837,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3802,41 +3850,41 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>Burkardt</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3854,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3863,10 +3911,10 @@
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -3878,41 +3926,41 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Atubolu</t>
+          <t>Demirovic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3921,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -3930,22 +3978,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3958,13 +4006,13 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -3973,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -3982,12 +4030,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Neuer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3997,7 +4045,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -4010,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -4034,12 +4082,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tah</t>
+          <t>Urbig</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4049,14 +4097,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -4077,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4086,26 +4134,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -4114,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4123,13 +4171,13 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -4138,26 +4186,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Honorat</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4169,47 +4217,47 @@
         <v>2.5</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Quansah</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -4218,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -4230,29 +4278,29 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nwaneri</t>
+          <t>Avdullahu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4270,19 +4318,19 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -4294,17 +4342,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Suzuki</t>
+          <t>Führich</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4322,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4346,22 +4394,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Füllkrug</t>
+          <t>Kai. Sano</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -4374,13 +4422,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4398,22 +4446,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mokwa</t>
+          <t>Khedira</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -4426,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -4450,26 +4498,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vandevoordt</t>
+          <t>M. Eggestein</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -4481,10 +4529,10 @@
         <v>2.5</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4493,14 +4541,1262 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Musiala</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Petkov</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Prömel</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ebnoutalib</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Schick</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Leverkusen</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Undav</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Atubolu</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>10</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Baku</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Schlotterbeck</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Svensson</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tah</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ABW</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>El Aynaoui</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fabio Vieira</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HSV</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Honorat</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Gladbach</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nwaneri</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Suzuki</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Veerman</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Füllkrug</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Luis Diaz</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mokwa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Saibari</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Vandevoordt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
         <v>6</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N91" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N67"/>
+  <autoFilter ref="A1:N91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabelle'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorie-Profil'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,22 +476,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Fischköppe</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>62.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38.5</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.5</v>
+        <v>55.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -548,22 +548,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fischköppe</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -635,6 +635,8 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -655,40 +657,56 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ST 4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kum. ST 4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>26.5</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5</v>
+        <v>62.5</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>13.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>62.5</v>
       </c>
     </row>
     <row r="3">
@@ -704,57 +722,75 @@
         <v>18.5</v>
       </c>
       <c r="D3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
         <v>38.5</v>
       </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>38.5</v>
+      <c r="H3" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="n">
-        <v>37.5</v>
+        <v>16.5</v>
       </c>
       <c r="E4" t="n">
-        <v>23.5</v>
+        <v>55.5</v>
       </c>
       <c r="F4" t="n">
-        <v>37.5</v>
+        <v>17.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="n">
+        <v>55.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="E5" t="n">
-        <v>13.5</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>23.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -770,13 +806,19 @@
         <v>14.5</v>
       </c>
       <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G6" t="n">
         <v>33</v>
       </c>
-      <c r="E6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>33</v>
+      <c r="H6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -792,17 +834,23 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
         <v>26</v>
       </c>
-      <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>26</v>
+      <c r="H7" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -865,26 +913,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="3">
@@ -894,72 +942,72 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="C3" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="G3" t="n">
-        <v>38.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="D4" t="n">
         <v>9.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>37.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -969,22 +1017,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D6" t="n">
         <v>8.5</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -994,22 +1042,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1185,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1146,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1155,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -1279,7 +1327,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Upamecano</t>
+          <t>Stanisic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1293,7 +1341,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1302,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1317,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1331,30 +1379,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Upamecano</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1369,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1383,12 +1431,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Doan</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1397,16 +1445,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1415,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1435,12 +1483,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E. Fernandez</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1449,7 +1497,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1458,25 +1506,25 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1487,12 +1535,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>E. Fernandez</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1501,22 +1549,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1528,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1539,12 +1587,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kimmich</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1553,16 +1601,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1591,12 +1639,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mohya</t>
+          <t>Kimmich</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1605,16 +1653,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1643,30 +1691,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gregoritsch</t>
+          <t>Mohya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1695,12 +1743,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Gregoritsch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1709,7 +1757,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1718,13 +1766,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1747,12 +1795,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Matanovic</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1761,7 +1809,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1770,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2.83</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1799,7 +1847,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Backhaus</t>
+          <t>Matanovic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1809,7 +1857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1822,13 +1870,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1840,32 +1888,32 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lukeba</t>
+          <t>Backhaus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1874,22 +1922,22 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1903,12 +1951,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Lukeba</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1917,7 +1965,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1926,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1935,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1955,12 +2003,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mittelstädt</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1969,7 +2017,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1978,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1987,16 +2035,16 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2007,7 +2055,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vagnoman</t>
+          <t>Mittelstädt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2021,7 +2069,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2030,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2045,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2059,17 +2107,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>Vagnoman</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2082,25 +2130,25 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2111,7 +2159,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Karetsas</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2125,22 +2173,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2152,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2163,12 +2211,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S. El Mala</t>
+          <t>Karaman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2183,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2215,12 +2263,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stiller</t>
+          <t>Karetsas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2238,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2267,12 +2315,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>S. El Mala</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2290,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2299,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2319,12 +2367,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wimmer</t>
+          <t>Stiller</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2342,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2371,17 +2419,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guirassy</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2391,19 +2439,19 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -2423,21 +2471,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pejcinovic</t>
+          <t>Wimmer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2446,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2475,21 +2523,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Flekken</t>
+          <t>Guirassy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2498,19 +2546,19 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2527,21 +2575,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zentner</t>
+          <t>Pejcinovic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2550,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2565,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2574,22 +2622,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Romulo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2602,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2617,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2626,22 +2674,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jeltsch</t>
+          <t>Flekken</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2654,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2663,13 +2711,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2678,26 +2726,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lienhart</t>
+          <t>Zentner</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2721,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2735,12 +2783,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Simpson-Pusey</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2749,7 +2797,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2758,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2773,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2787,17 +2835,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Jeltsch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2810,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2819,13 +2867,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2839,21 +2887,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Lienhart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2862,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2877,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2891,17 +2939,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grönbaek</t>
+          <t>Simpson-Pusey</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2914,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2929,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2943,12 +2991,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2957,7 +3005,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2969,10 +3017,10 @@
         <v>3.5</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2995,12 +3043,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Leweling</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3009,16 +3057,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3047,12 +3095,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Onyeka</t>
+          <t>Grönbaek</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3061,7 +3109,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3070,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3079,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3099,21 +3147,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lemperle</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3122,13 +3170,13 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3151,36 +3199,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nkunku</t>
+          <t>Leweling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3203,30 +3251,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Olise</t>
+          <t>Onyeka</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3255,17 +3303,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kobel</t>
+          <t>Lemperle</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3281,10 +3329,10 @@
         <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3293,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3302,22 +3350,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Laimer</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3330,13 +3378,13 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3354,26 +3402,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>Olise</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -3382,36 +3430,36 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ryerson</t>
+          <t>Kobel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3421,11 +3469,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3434,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3449,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3463,12 +3511,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tapsoba</t>
+          <t>Gadou</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3477,16 +3525,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3495,13 +3543,13 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3515,17 +3563,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aleix Garcia</t>
+          <t>Laimer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3567,17 +3615,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Raum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3590,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3619,21 +3667,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>El Khannouss</t>
+          <t>Ryerson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3642,13 +3690,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3657,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3671,21 +3719,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gruda</t>
+          <t>Tapsoba</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3694,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3703,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3723,7 +3771,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>Aleix Garcia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3746,13 +3794,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3764,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3775,12 +3823,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pavlovic</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3789,7 +3837,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3807,10 +3855,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3827,12 +3875,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Uzun</t>
+          <t>El Khannouss</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3841,7 +3889,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3850,13 +3898,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -3868,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3879,21 +3927,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Burkardt</t>
+          <t>Gruda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3902,13 +3950,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -3931,36 +3979,36 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Demirovic</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2.17</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3972,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3983,21 +4031,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Pavlovic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4006,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4015,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -4035,21 +4083,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Neuer</t>
+          <t>Uzun</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4061,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4076,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4087,24 +4135,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Urbig</t>
+          <t>Burkardt</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -4113,10 +4161,10 @@
         <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4125,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4134,22 +4182,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Demirovic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -4159,25 +4207,25 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -4186,12 +4234,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4201,7 +4249,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -4214,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4229,31 +4277,31 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quansah</t>
+          <t>Neuer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -4275,56 +4323,56 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Avdullahu</t>
+          <t>Urbig</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -4333,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -4347,21 +4395,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Führich</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -4370,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4379,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -4399,21 +4447,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kai. Sano</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4422,13 +4470,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4437,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4451,21 +4499,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Khedira</t>
+          <t>Quansah</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -4474,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -4483,16 +4531,16 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4503,21 +4551,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>M. Eggestein</t>
+          <t>R. Koch</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -4526,22 +4574,22 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -4555,12 +4603,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Musiala</t>
+          <t>Avdullahu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4578,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -4607,12 +4655,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Petkov</t>
+          <t>Führich</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4621,7 +4669,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -4630,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4639,10 +4687,10 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4659,12 +4707,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Prömel</t>
+          <t>Kai. Sano</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4673,7 +4721,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4682,13 +4730,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4711,17 +4759,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ebnoutalib</t>
+          <t>Khedira</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -4743,10 +4791,10 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4763,21 +4811,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>M. Eggestein</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4786,19 +4834,19 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="I72" t="n">
         <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4815,17 +4863,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Undav</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -4838,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4867,17 +4915,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Atubolu</t>
+          <t>Musiala</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4890,22 +4938,22 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -4914,50 +4962,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Petkov</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -4966,26 +5014,26 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Prömel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -4994,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -5018,22 +5066,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Schlotterbeck</t>
+          <t>Ebnoutalib</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -5046,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5055,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -5070,22 +5118,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Hlozek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -5098,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -5122,26 +5170,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tah</t>
+          <t>Schick</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -5150,19 +5198,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5174,22 +5222,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>El Aynaoui</t>
+          <t>Undav</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -5202,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -5226,26 +5274,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Atubolu</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -5254,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5269,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -5283,45 +5331,45 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Honorat</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -5335,21 +5383,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -5367,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -5387,21 +5435,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nwaneri</t>
+          <t>Kabak</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -5410,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -5419,13 +5467,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5439,17 +5487,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Suzuki</t>
+          <t>Schlotterbeck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -5462,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -5491,7 +5539,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Veerman</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5501,7 +5549,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -5514,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -5543,21 +5591,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Füllkrug</t>
+          <t>Tah</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5566,13 +5614,13 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -5595,21 +5643,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Luis Diaz</t>
+          <t>El Aynaoui</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -5618,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -5647,17 +5695,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mokwa</t>
+          <t>Fabio Vieira</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -5670,13 +5718,13 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -5699,21 +5747,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Saibari</t>
+          <t>Honorat</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -5731,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5751,52 +5799,468 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nwaneri</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Suzuki</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Veerman</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Füllkrug</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Luis Diaz</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mokwa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Saibari</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>Vandevoordt</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>6</v>
-      </c>
-      <c r="N91" t="n">
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>10</v>
+      </c>
+      <c r="N99" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N91"/>
+  <autoFilter ref="A1:N99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verlauf" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kategorie-Profil" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spieler-Beiträge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abrechnung" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabelle'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorie-Profil'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Abrechnung'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,13 +487,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +511,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +526,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55.5</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -548,22 +550,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>69.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -605,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>55.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -637,6 +639,8 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,22 +666,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>ST 5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>kum. ST 5</t>
         </is>
       </c>
     </row>
@@ -697,16 +711,22 @@
         <v>26.5</v>
       </c>
       <c r="E2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I2" t="n">
         <v>62.5</v>
       </c>
-      <c r="F2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H2" t="n">
-        <v>62.5</v>
+      <c r="J2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -725,100 +745,124 @@
         <v>17.5</v>
       </c>
       <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>56</v>
       </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>56</v>
+      <c r="J3" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>55.5</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>17.5</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>18.5</v>
       </c>
       <c r="H4" t="n">
-        <v>55.5</v>
+        <v>33</v>
+      </c>
+      <c r="I4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="C5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E5" t="n">
         <v>14</v>
       </c>
-      <c r="D5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
-      </c>
       <c r="F5" t="n">
-        <v>23.5</v>
+        <v>69.5</v>
       </c>
       <c r="G5" t="n">
-        <v>37.5</v>
+        <v>17.5</v>
       </c>
       <c r="H5" t="n">
-        <v>52</v>
+        <v>39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>69.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
         <v>14.5</v>
       </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>18.5</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>33</v>
+        <v>23.5</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>37.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>52</v>
+      </c>
+      <c r="J6" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -837,20 +881,26 @@
         <v>18</v>
       </c>
       <c r="E7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" t="n">
         <v>44</v>
       </c>
-      <c r="F7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" t="n">
-        <v>26</v>
-      </c>
-      <c r="H7" t="n">
-        <v>44</v>
+      <c r="J7" t="n">
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -917,22 +967,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="G2" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -942,97 +992,97 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="F3" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
         <v>13.5</v>
       </c>
-      <c r="D4" t="n">
-        <v>9.5</v>
-      </c>
       <c r="E4" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>55.5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1042,22 +1092,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="E7" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
@@ -1072,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1185,31 +1235,31 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1237,7 +1287,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1255,13 +1305,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1393,17 +1443,17 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.17</v>
-      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1417,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1445,7 +1495,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1454,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1497,7 +1547,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1506,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1653,7 +1703,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1662,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1705,7 +1755,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1714,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1743,30 +1793,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gregoritsch</t>
+          <t>Seiwald</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1795,12 +1845,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Gregoritsch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1809,7 +1859,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1818,13 +1868,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1836,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1847,12 +1897,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Matanovic</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1861,7 +1911,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1870,19 +1920,19 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1899,7 +1949,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Backhaus</t>
+          <t>Matanovic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1909,7 +1959,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1922,13 +1972,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1937,35 +1987,35 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lukeba</t>
+          <t>Backhaus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1974,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1989,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2003,12 +2053,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Lukeba</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2017,7 +2067,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2026,25 +2076,25 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2055,12 +2105,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mittelstädt</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2069,34 +2119,34 @@
         </is>
       </c>
       <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2107,7 +2157,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vagnoman</t>
+          <t>Mittelstädt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2121,16 +2171,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2145,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2159,17 +2209,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>Vagnoman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2182,25 +2232,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2211,12 +2261,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Karaman</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2225,22 +2275,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2252,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2263,12 +2313,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karetsas</t>
+          <t>Karaman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2286,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2315,12 +2365,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S. El Mala</t>
+          <t>Karetsas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2329,7 +2379,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2338,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2367,12 +2417,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stiller</t>
+          <t>S. El Mala</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2381,22 +2431,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2419,12 +2469,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>Stiller</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2433,16 +2483,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.25</v>
+        <v>2.67</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2451,16 +2501,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2471,12 +2521,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wimmer</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2485,16 +2535,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>3.33</v>
+        <v>4.25</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2503,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2523,17 +2573,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guirassy</t>
+          <t>Wimmer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2546,19 +2596,19 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.67</v>
+        <v>3.33</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2575,12 +2625,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pejcinovic</t>
+          <t>Guirassy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2589,7 +2639,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2598,19 +2648,19 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2627,12 +2677,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Romulo</t>
+          <t>Pejcinovic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2641,7 +2691,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2650,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2679,17 +2729,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Flekken</t>
+          <t>Romulo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2702,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2711,10 +2761,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2731,12 +2781,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zentner</t>
+          <t>Flekken</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2745,7 +2795,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2754,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2778,26 +2828,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Zentner</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2806,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2821,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2835,12 +2885,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jeltsch</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2849,16 +2899,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2867,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2887,12 +2937,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lienhart</t>
+          <t>Jeltsch</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2901,31 +2951,31 @@
         </is>
       </c>
       <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
         <v>3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2939,12 +2989,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Simpson-Pusey</t>
+          <t>Lienhart</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2953,7 +3003,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2962,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2991,17 +3041,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Simpson-Pusey</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3014,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3029,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3043,12 +3093,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3057,7 +3107,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3066,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3075,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3095,12 +3145,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Grönbaek</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3109,7 +3159,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3118,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.83</v>
+        <v>3.12</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3127,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3147,12 +3197,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Grönbaek</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3161,7 +3211,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3170,19 +3220,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3199,12 +3249,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Leweling</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3213,7 +3263,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3222,13 +3272,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3251,12 +3301,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Onyeka</t>
+          <t>Leweling</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3265,16 +3315,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3303,36 +3353,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lemperle</t>
+          <t>Onyeka</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3355,7 +3405,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nkunku</t>
+          <t>Reitz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3365,7 +3415,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3375,16 +3425,16 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3407,12 +3457,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Olise</t>
+          <t>Lemperle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3430,25 +3480,25 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>3.17</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3459,21 +3509,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kobel</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3482,13 +3532,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3497,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3506,78 +3556,78 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gadou</t>
+          <t>Olise</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Laimer</t>
+          <t>Kobel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -3586,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3601,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3615,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>Gadou</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3629,16 +3679,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3653,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3667,12 +3717,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ryerson</t>
+          <t>Laimer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3681,31 +3731,31 @@
         </is>
       </c>
       <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>3</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3719,12 +3769,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tapsoba</t>
+          <t>Raum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3733,17 +3783,17 @@
         </is>
       </c>
       <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
         <v>3</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.67</v>
-      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -3751,13 +3801,13 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3771,21 +3821,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aleix Garcia</t>
+          <t>Ryerson</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3794,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3809,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3823,21 +3873,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Tapsoba</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3846,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3855,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3875,12 +3925,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>El Khannouss</t>
+          <t>Aleix Garcia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3889,7 +3939,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3898,19 +3948,19 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3927,12 +3977,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gruda</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3941,7 +3991,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3950,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3979,12 +4029,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>El Khannouss</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3993,16 +4043,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>2.17</v>
+        <v>3.75</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -4020,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4031,12 +4081,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pavlovic</t>
+          <t>Gruda</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4045,7 +4095,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4054,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4063,10 +4113,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -4083,12 +4133,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Uzun</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4097,7 +4147,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4106,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4135,21 +4185,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Burkardt</t>
+          <t>Pavlovic</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4161,16 +4211,16 @@
         <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4187,33 +4237,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Demirovic</t>
+          <t>Uzun</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>2</v>
@@ -4228,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -4239,12 +4289,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Burkardt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4253,7 +4303,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4262,13 +4312,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4291,17 +4341,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Neuer</t>
+          <t>Demirovic</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -4311,16 +4361,16 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -4343,24 +4393,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Urbig</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4369,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -4381,35 +4431,35 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Neuer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -4418,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4427,13 +4477,13 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -4442,41 +4492,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Urbig</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>3</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2.33</v>
-      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4488,7 +4538,7 @@
         <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4499,12 +4549,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quansah</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4522,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -4537,10 +4587,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4551,12 +4601,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R. Koch</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4565,7 +4615,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -4574,25 +4624,25 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4603,21 +4653,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Avdullahu</t>
+          <t>Quansah</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -4626,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -4635,16 +4685,16 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4655,21 +4705,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Führich</t>
+          <t>R. Koch</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -4678,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4687,13 +4737,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4707,12 +4757,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kai. Sano</t>
+          <t>Avdullahu</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4721,7 +4771,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4730,13 +4780,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4759,12 +4809,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Khedira</t>
+          <t>Führich</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4773,7 +4823,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -4782,13 +4832,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>4.5</v>
+        <v>3.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4811,12 +4861,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>M. Eggestein</t>
+          <t>Kai. Sano</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4825,7 +4875,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4834,13 +4884,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -4863,12 +4913,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Khedira</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4877,7 +4927,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4886,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4915,12 +4965,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Musiala</t>
+          <t>M. Eggestein</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4929,7 +4979,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -4938,19 +4988,19 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4967,12 +5017,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Petkov</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4990,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -4999,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -5019,12 +5069,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prömel</t>
+          <t>Musiala</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5051,10 +5101,10 @@
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5071,21 +5121,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ebnoutalib</t>
+          <t>Petkov</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -5094,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5106,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -5123,21 +5173,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hlozek</t>
+          <t>Prömel</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -5146,13 +5196,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -5175,12 +5225,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>Ebnoutalib</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5189,7 +5239,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -5198,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -5227,12 +5277,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Undav</t>
+          <t>Hlozek</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5241,7 +5291,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -5250,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -5279,21 +5329,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Atubolu</t>
+          <t>Schick</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -5302,65 +5352,65 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Undav</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -5369,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -5378,26 +5428,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Atubolu</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -5406,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -5421,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -5435,12 +5485,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kabak</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5449,22 +5499,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>4.5</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -5487,12 +5537,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Schlotterbeck</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5501,7 +5551,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5510,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -5539,12 +5589,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Kabak</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5553,7 +5603,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -5562,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -5577,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -5591,12 +5641,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tah</t>
+          <t>Schlotterbeck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5605,7 +5655,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5614,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -5629,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -5643,21 +5693,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>El Aynaoui</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -5666,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -5695,21 +5745,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Tah</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -5718,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>2.83</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -5733,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -5747,12 +5797,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Honorat</t>
+          <t>Beste</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5761,7 +5811,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -5770,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -5779,10 +5829,10 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5799,12 +5849,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>El Aynaoui</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5822,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -5851,12 +5901,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nwaneri</t>
+          <t>Fabio Vieira</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5865,7 +5915,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -5874,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -5883,10 +5933,10 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -5903,12 +5953,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Suzuki</t>
+          <t>Honorat</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5917,7 +5967,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -5926,19 +5976,19 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -5955,12 +6005,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Veerman</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5969,7 +6019,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -5978,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -5987,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -6007,21 +6057,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Füllkrug</t>
+          <t>Nwaneri</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -6030,19 +6080,19 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>3.17</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -6059,21 +6109,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Luis Diaz</t>
+          <t>Suzuki</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -6082,13 +6132,13 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -6111,42 +6161,42 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mokwa</t>
+          <t>Veerman</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>3.83</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -6163,12 +6213,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Saibari</t>
+          <t>Füllkrug</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6177,7 +6227,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -6186,19 +6236,19 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -6215,17 +6265,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vandevoordt</t>
+          <t>Luis Diaz</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -6238,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>2.83</v>
+        <v>3.83</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -6253,14 +6303,453 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mokwa</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Saibari</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Vandevoordt</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>10</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
+      <c r="N102" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N99"/>
+  <autoFilter ref="A1:N102"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Platz</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spieltagssiege</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Siegprämien €</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Platzierungsprämie € (Vorschau)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Einsatz bisher €</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Saldo bisher €</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Saisonende € (Vorschau)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fischköppe</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Käsefüße</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vickings</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-10.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Great Licors</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hallodries</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hansa Fürze</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1 € je Manager und Spieltag (4 von 33 gewertet), Topf 198.0 €; 3.0 € je Spieltagssieg (geteilt anteilig); Meisterschaftstopf 99.0 €: 1. Platz 49.5 €, 2. Platz 29.7 €, 3. Platz 19.8 €; Auszahlung am Saisonende, Kassenwart Martin</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabelle'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorie-Profil'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Abrechnung'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -502,22 +502,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Käsefüße</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>92.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -526,22 +526,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>90.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -550,22 +550,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69.5</v>
+        <v>86.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -574,22 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Käsefüße</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55.5</v>
+        <v>70.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,8 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,27 +673,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>ST 6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kum. ST 6</t>
         </is>
       </c>
     </row>
@@ -714,155 +726,185 @@
         <v>17.5</v>
       </c>
       <c r="F2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2" t="n">
+        <v>103</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K2" t="n">
         <v>80</v>
       </c>
-      <c r="G2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36</v>
-      </c>
-      <c r="I2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>80</v>
+      <c r="L2" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>23.5</v>
       </c>
       <c r="C3" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>24.5</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>92.5</v>
       </c>
       <c r="H3" t="n">
-        <v>38.5</v>
+        <v>23.5</v>
       </c>
       <c r="I3" t="n">
-        <v>56</v>
+        <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>76</v>
+        <v>52</v>
+      </c>
+      <c r="K3" t="n">
+        <v>68</v>
+      </c>
+      <c r="L3" t="n">
+        <v>92.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="C4" t="n">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>18.5</v>
+        <v>90.5</v>
       </c>
       <c r="H4" t="n">
-        <v>33</v>
+        <v>17.5</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J4" t="n">
-        <v>71</v>
+        <v>55.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>90.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="C5" t="n">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>69.5</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5</v>
+        <v>86.5</v>
       </c>
       <c r="H5" t="n">
-        <v>39</v>
+        <v>18.5</v>
       </c>
       <c r="I5" t="n">
-        <v>55.5</v>
+        <v>33</v>
       </c>
       <c r="J5" t="n">
-        <v>69.5</v>
+        <v>45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>71</v>
+      </c>
+      <c r="L5" t="n">
+        <v>86.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>23.5</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>52</v>
+        <v>38.5</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="K6" t="n">
+        <v>76</v>
+      </c>
+      <c r="L6" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -884,23 +926,29 @@
         <v>11.5</v>
       </c>
       <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44</v>
+      </c>
+      <c r="K7" t="n">
         <v>55.5</v>
       </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>26</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44</v>
-      </c>
-      <c r="J7" t="n">
-        <v>55.5</v>
+      <c r="L7" t="n">
+        <v>70.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -967,122 +1015,122 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>20.5</v>
       </c>
       <c r="C3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>15</v>
       </c>
-      <c r="C4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.5</v>
-      </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>69.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
         <v>15.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
       <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F6" t="n">
         <v>19</v>
       </c>
-      <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="G6" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -1092,22 +1140,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="D7" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
-        <v>55.5</v>
+        <v>70.5</v>
       </c>
     </row>
   </sheetData>
@@ -1122,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1287,16 +1335,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1311,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1391,7 +1439,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1400,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1415,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -1443,34 +1491,34 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1495,7 +1543,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1504,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1547,7 +1595,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1599,7 +1647,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1608,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1651,7 +1699,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1660,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1703,7 +1751,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1712,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1721,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1845,12 +1893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gregoritsch</t>
+          <t>Beier</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1868,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1897,12 +1945,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Gregoritsch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1911,34 +1959,34 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1949,12 +1997,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Matanovic</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1963,7 +2011,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1972,25 +2020,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2001,7 +2049,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Backhaus</t>
+          <t>Matanovic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2011,27 +2059,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -2039,35 +2087,35 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lukeba</t>
+          <t>Backhaus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2076,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2091,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2100,53 +2148,53 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Seimen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2157,12 +2205,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mittelstädt</t>
+          <t>Lukeba</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2171,7 +2219,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2180,22 +2228,22 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2209,12 +2257,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vagnoman</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2223,34 +2271,34 @@
         </is>
       </c>
       <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2261,48 +2309,48 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>Mittelstädt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2313,45 +2361,45 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karaman</t>
+          <t>Vagnoman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2365,7 +2413,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Karetsas</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2379,22 +2427,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.17</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2406,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2417,12 +2465,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S. El Mala</t>
+          <t>Grifo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2431,7 +2479,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2440,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2469,12 +2517,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stiller</t>
+          <t>Karaman</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2492,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.67</v>
+        <v>4.17</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2501,16 +2549,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2521,12 +2569,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>Karetsas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2535,7 +2583,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2544,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2553,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2573,12 +2621,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wimmer</t>
+          <t>S. El Mala</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2587,22 +2635,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>3.33</v>
+        <v>4.12</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2625,17 +2673,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Guirassy</t>
+          <t>Stiller</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2651,22 +2699,22 @@
         <v>2.75</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2677,17 +2725,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pejcinovic</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2697,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2709,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2729,21 +2777,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Romulo</t>
+          <t>Wimmer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2752,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2761,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2781,21 +2829,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Flekken</t>
+          <t>Asllani</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2804,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2819,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2833,21 +2881,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zentner</t>
+          <t>Guirassy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2856,22 +2904,22 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2880,35 +2928,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Pejcinovic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2923,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2932,22 +2980,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jeltsch</t>
+          <t>Romulo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2960,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2975,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2984,22 +3032,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lienhart</t>
+          <t>Flekken</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3012,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3027,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3036,36 +3084,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Simpson-Pusey</t>
+          <t>Zentner</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4.33</v>
-      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -3079,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3093,30 +3141,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3125,13 +3173,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3145,45 +3193,45 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Jeltsch</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
         <v>4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3197,21 +3245,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Grönbaek</t>
+          <t>Lienhart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3220,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3229,13 +3277,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3249,36 +3297,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Simpson-Pusey</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3287,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3301,12 +3349,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Leweling</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3315,16 +3363,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>4.17</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3333,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3353,12 +3401,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Onyeka</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3367,16 +3415,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3405,12 +3453,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reitz</t>
+          <t>Grönbaek</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3419,16 +3467,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.5</v>
+        <v>3.83</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3437,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3457,36 +3505,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lemperle</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>3.17</v>
+        <v>3.88</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3509,36 +3557,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nkunku</t>
+          <t>Leweling</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3561,48 +3609,48 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Olise</t>
+          <t>Onyeka</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.88</v>
+        <v>4.25</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3613,30 +3661,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kobel</t>
+          <t>Reitz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3651,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3660,41 +3708,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gadou</t>
+          <t>Lemperle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3703,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3712,22 +3760,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laimer</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3737,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3755,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3764,26 +3812,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>Olise</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3792,36 +3840,36 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>8</v>
+      </c>
+      <c r="K51" t="n">
         <v>3</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ryerson</t>
+          <t>Kobel</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3831,11 +3879,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3844,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3859,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3873,12 +3921,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tapsoba</t>
+          <t>Gadou</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3887,16 +3935,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3905,13 +3953,13 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3925,17 +3973,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aleix Garcia</t>
+          <t>Laimer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3945,10 +3993,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3957,13 +4005,13 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3977,17 +4025,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Raum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -4000,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -4029,36 +4077,36 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>El Khannouss</t>
+          <t>Ryerson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4067,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -4081,21 +4129,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gruda</t>
+          <t>Tapsoba</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4104,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4113,13 +4161,13 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -4133,7 +4181,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>Aleix Garcia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4156,25 +4204,25 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4185,12 +4233,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pavlovic</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4199,7 +4247,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4208,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -4217,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4237,12 +4285,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Uzun</t>
+          <t>El Khannouss</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4251,22 +4299,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4278,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4289,21 +4337,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Burkardt</t>
+          <t>Gruda</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4312,13 +4360,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3.67</v>
+        <v>2.75</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4341,48 +4389,48 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Demirovic</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4393,21 +4441,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Pavlovic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -4416,19 +4464,19 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -4445,36 +4493,36 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Neuer</t>
+          <t>Uzun</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4483,10 +4531,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4497,36 +4545,36 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Urbig</t>
+          <t>Burkardt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4535,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -4544,22 +4592,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Demirovic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -4569,25 +4617,25 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -4596,12 +4644,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4611,7 +4659,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -4624,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4639,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
@@ -4648,87 +4696,87 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Quansah</t>
+          <t>Neuer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>4</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" t="n">
-        <v>5</v>
-      </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R. Koch</t>
+          <t>Urbig</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4737,13 +4785,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4757,21 +4805,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Avdullahu</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4780,25 +4828,25 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4809,21 +4857,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Führich</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -4832,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -4847,10 +4895,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4861,21 +4909,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kai. Sano</t>
+          <t>Quansah</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4884,25 +4932,25 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4913,21 +4961,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Khedira</t>
+          <t>R. Koch</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4936,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4945,13 +4993,13 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -4965,12 +5013,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>M. Eggestein</t>
+          <t>Avdullahu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4988,13 +5036,13 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -5017,12 +5065,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Führich</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5031,22 +5079,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>3.75</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -5069,12 +5117,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Musiala</t>
+          <t>Kai. Sano</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5086,25 +5134,25 @@
         <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5121,12 +5169,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Petkov</t>
+          <t>Khedira</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5153,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -5173,12 +5221,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prömel</t>
+          <t>M. Eggestein</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5187,7 +5235,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -5196,13 +5244,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -5225,21 +5273,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ebnoutalib</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -5248,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -5257,10 +5305,10 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5277,17 +5325,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hlozek</t>
+          <t>Musiala</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -5300,19 +5348,19 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -5329,17 +5377,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>Petkov</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -5352,25 +5400,25 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
         <v>4</v>
       </c>
-      <c r="J81" t="n">
-        <v>8</v>
-      </c>
-      <c r="K81" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>2</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5381,7 +5429,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Undav</t>
+          <t>Prömel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5391,11 +5439,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -5404,13 +5452,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -5433,7 +5481,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Atubolu</t>
+          <t>Ebnoutalib</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5443,11 +5491,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -5456,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -5465,13 +5513,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -5480,50 +5528,50 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Hlozek</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5532,26 +5580,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Schick</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5560,50 +5608,50 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kabak</t>
+          <t>Undav</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -5612,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -5627,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -5636,26 +5684,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Schlotterbeck</t>
+          <t>Atubolu</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5664,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.67</v>
+        <v>3.7</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -5679,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -5693,12 +5741,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5707,22 +5755,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -5731,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
@@ -5745,7 +5793,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tah</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5759,7 +5807,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -5768,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -5783,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -5797,30 +5845,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Beste</t>
+          <t>Kabak</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -5835,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -5849,21 +5897,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>El Aynaoui</t>
+          <t>Schlotterbeck</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -5872,22 +5920,22 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5901,21 +5949,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -5924,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -5953,21 +6001,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Honorat</t>
+          <t>Tah</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -5976,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -5985,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -6005,12 +6053,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Beste</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6019,7 +6067,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -6037,10 +6085,10 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -6057,12 +6105,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nwaneri</t>
+          <t>El Aynaoui</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6071,7 +6119,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -6080,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -6109,12 +6157,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Suzuki</t>
+          <t>Fabio Vieira</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6123,22 +6171,22 @@
         </is>
       </c>
       <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>4</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>3.25</v>
-      </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -6161,12 +6209,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Veerman</t>
+          <t>Honorat</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6175,16 +6223,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -6193,10 +6241,10 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -6213,21 +6261,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Füllkrug</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -6236,19 +6284,19 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -6265,21 +6313,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Luis Diaz</t>
+          <t>Nwaneri</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -6288,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -6297,10 +6345,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -6317,21 +6365,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mokwa</t>
+          <t>Suzuki</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -6340,13 +6388,13 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -6369,42 +6417,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Saibari</t>
+          <t>Veerman</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -6421,52 +6469,260 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>Füllkrug</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Luis Diaz</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>6</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Mokwa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Saibari</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>Vandevoordt</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>4</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>10</v>
-      </c>
-      <c r="N102" t="n">
+      <c r="E106" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>22</v>
+      </c>
+      <c r="N106" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N102"/>
+  <autoFilter ref="A1:N106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6562,10 +6818,10 @@
         <v>49.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="I2" t="n">
         <v>22.5</v>
@@ -6577,31 +6833,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Käsefüße</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>29.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>25.7</v>
+        <v>30.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -6610,31 +6866,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>19.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>18.8</v>
+        <v>14.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.2</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="5">
@@ -6643,31 +6899,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="I5" t="n">
-        <v>-33</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="6">
@@ -6676,31 +6932,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Käsefüße</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="I6" t="n">
-        <v>-30</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="7">
@@ -6727,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I7" t="n">
         <v>-33</v>
@@ -6744,7 +7000,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 € je Manager und Spieltag (4 von 33 gewertet), Topf 198.0 €; 3.0 € je Spieltagssieg (geteilt anteilig); Meisterschaftstopf 99.0 €: 1. Platz 49.5 €, 2. Platz 29.7 €, 3. Platz 19.8 €; Auszahlung am Saisonende, Kassenwart Martin</t>
+          <t>1 € je Manager und Spieltag (5 von 33 gewertet), Topf 198.0 €; 3.0 € je Spieltagssieg (geteilt anteilig); Meisterschaftstopf 99.0 €: 1. Platz 49.5 €, 2. Platz 29.7 €, 3. Platz 19.8 €; Auszahlung am Saisonende, Kassenwart Martin</t>
         </is>
       </c>
     </row>

--- a/daten/saison.xlsx
+++ b/daten/saison.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabelle'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Verlauf'!$A$1:$N$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorie-Profil'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spieler-Beiträge'!$A$1:$N$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Abrechnung'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -502,22 +502,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>92.5</v>
+        <v>111.5</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -526,22 +526,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90.5</v>
+        <v>107</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -550,22 +550,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>86.5</v>
+        <v>105</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>94.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70.5</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,8 @@
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,32 +680,42 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>ST 7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>kum. ST 6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>kum. ST 7</t>
         </is>
       </c>
     </row>
@@ -729,142 +741,166 @@
         <v>23</v>
       </c>
       <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>122</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>80</v>
+      </c>
+      <c r="M2" t="n">
         <v>103</v>
       </c>
-      <c r="H2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>80</v>
-      </c>
-      <c r="L2" t="n">
-        <v>103</v>
+      <c r="N2" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>24.5</v>
+        <v>15.5</v>
       </c>
       <c r="G3" t="n">
-        <v>92.5</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>23.5</v>
+        <v>111.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>18.5</v>
       </c>
       <c r="J3" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="K3" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="L3" t="n">
-        <v>92.5</v>
+        <v>71</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>111.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.5</v>
+        <v>23.5</v>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>24.5</v>
       </c>
       <c r="G4" t="n">
-        <v>90.5</v>
+        <v>14.5</v>
       </c>
       <c r="H4" t="n">
-        <v>17.5</v>
+        <v>107</v>
       </c>
       <c r="I4" t="n">
-        <v>39</v>
+        <v>23.5</v>
       </c>
       <c r="J4" t="n">
-        <v>55.5</v>
+        <v>37.5</v>
       </c>
       <c r="K4" t="n">
-        <v>69.5</v>
+        <v>52</v>
       </c>
       <c r="L4" t="n">
-        <v>90.5</v>
+        <v>68</v>
+      </c>
+      <c r="M4" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="C5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G5" t="n">
         <v>14.5</v>
       </c>
-      <c r="D5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>86.5</v>
-      </c>
       <c r="H5" t="n">
-        <v>18.5</v>
+        <v>105</v>
       </c>
       <c r="I5" t="n">
-        <v>33</v>
+        <v>17.5</v>
       </c>
       <c r="J5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>55.5</v>
       </c>
       <c r="L5" t="n">
-        <v>86.5</v>
+        <v>69.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -889,22 +925,28 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>56</v>
+      </c>
+      <c r="L6" t="n">
+        <v>76</v>
+      </c>
+      <c r="M6" t="n">
         <v>82</v>
       </c>
-      <c r="H6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>76</v>
-      </c>
-      <c r="L6" t="n">
-        <v>82</v>
+      <c r="N6" t="n">
+        <v>94.5</v>
       </c>
     </row>
     <row r="7">
@@ -929,26 +971,32 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44</v>
+      </c>
+      <c r="L7" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="M7" t="n">
         <v>70.5</v>
       </c>
-      <c r="H7" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>26</v>
-      </c>
-      <c r="J7" t="n">
-        <v>44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>70.5</v>
+      <c r="N7" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1015,97 +1063,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.5</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5</v>
+        <v>21.5</v>
       </c>
       <c r="F3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="G3" t="n">
-        <v>92.5</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>26.5</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5</v>
+        <v>25.5</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="G4" t="n">
-        <v>90.5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="n">
         <v>18</v>
       </c>
-      <c r="C5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>86.5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -1115,22 +1163,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="7">
@@ -1140,22 +1188,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="C7" t="n">
-        <v>16.5</v>
+        <v>20.5</v>
       </c>
       <c r="D7" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F7" t="n">
         <v>15.5</v>
       </c>
-      <c r="F7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G7" t="n">
-        <v>70.5</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1170,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1283,31 +1331,31 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1439,16 +1487,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1463,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -1491,34 +1539,34 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1591,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1561,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1595,7 +1643,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1604,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1647,7 +1695,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1656,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1699,7 +1747,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1708,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1803,7 +1851,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1812,25 +1860,25 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1959,7 +2007,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2011,7 +2059,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2020,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
@@ -2167,7 +2215,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2176,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2191,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2205,12 +2253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lukeba</t>
+          <t>Bensebaini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2219,7 +2267,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2228,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2243,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2257,12 +2305,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Lukeba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2271,34 +2319,34 @@
         </is>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.7</v>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2309,12 +2357,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mittelstädt</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2323,16 +2371,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2341,16 +2389,16 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2361,7 +2409,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vagnoman</t>
+          <t>Mittelstädt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2375,16 +2423,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2399,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2413,21 +2461,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>Vagnoman</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -2436,25 +2484,25 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2465,12 +2513,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grifo</t>
+          <t>Baumgartner</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2491,10 +2539,10 @@
         <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2517,12 +2565,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Karaman</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2531,22 +2579,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.17</v>
+        <v>3.42</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2558,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2569,12 +2617,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karetsas</t>
+          <t>Grifo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2583,7 +2631,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2592,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.17</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2621,12 +2669,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S. El Mala</t>
+          <t>Karaman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2635,22 +2683,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2673,12 +2721,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stiller</t>
+          <t>Karetsas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2687,16 +2735,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2.75</v>
+        <v>4.17</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2705,16 +2753,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2725,12 +2773,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tillman</t>
+          <t>S. El Mala</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2739,7 +2787,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2748,19 +2796,19 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2777,12 +2825,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wimmer</t>
+          <t>Stiller</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2791,7 +2839,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2800,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2809,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2829,30 +2877,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Asllani</t>
+          <t>Tillman</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2861,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2881,21 +2929,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guirassy</t>
+          <t>Wimmer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2904,19 +2952,19 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2933,12 +2981,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pejcinovic</t>
+          <t>Asllani</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2947,7 +2995,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2956,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2985,12 +3033,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Romulo</t>
+          <t>Guirassy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2999,7 +3047,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3011,16 +3059,16 @@
         <v>3.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3037,21 +3085,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Flekken</t>
+          <t>Pejcinovic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3060,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.75</v>
+        <v>3.83</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3069,13 +3117,13 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3089,21 +3137,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zentner</t>
+          <t>Romulo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3112,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3121,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3136,35 +3184,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diks</t>
+          <t>Flekken</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3179,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3188,36 +3236,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jeltsch</t>
+          <t>Zentner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2.83</v>
-      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -3225,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3245,12 +3293,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lienhart</t>
+          <t>Diks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3259,16 +3307,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3283,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3297,12 +3345,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Simpson-Pusey</t>
+          <t>Jeltsch</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3320,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.12</v>
+        <v>3.25</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3329,13 +3377,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3349,21 +3397,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amiri</t>
+          <t>Lienhart</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3372,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3381,13 +3429,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3401,17 +3449,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Burger</t>
+          <t>Simpson-Pusey</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3421,10 +3469,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3439,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3453,12 +3501,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Grönbaek</t>
+          <t>Amiri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3467,7 +3515,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3476,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3485,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3505,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Burger</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3519,7 +3567,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -3528,13 +3576,13 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3557,12 +3605,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Leweling</t>
+          <t>Grönbaek</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3571,28 +3619,28 @@
         </is>
       </c>
       <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
         <v>4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3609,12 +3657,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Onyeka</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3623,22 +3671,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3661,12 +3709,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reitz</t>
+          <t>Leweling</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3675,7 +3723,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -3684,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3693,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3713,36 +3761,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lemperle</t>
+          <t>Onyeka</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>3.17</v>
+        <v>4.25</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3765,7 +3813,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nkunku</t>
+          <t>Reitz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3775,26 +3823,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>4.25</v>
+        <v>5.17</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3817,12 +3865,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Olise</t>
+          <t>Lemperle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3831,7 +3879,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3840,25 +3888,25 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3869,36 +3917,36 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kobel</t>
+          <t>Nkunku</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9</v>
+        <v>4.67</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3907,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3916,87 +3964,87 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gadou</t>
+          <t>Olise</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Laimer</t>
+          <t>Kobel</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3.67</v>
+        <v>2.83</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -4011,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4025,12 +4073,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>Gadou</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4039,16 +4087,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -4063,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4077,12 +4125,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ryerson</t>
+          <t>Laimer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4097,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -4115,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -4129,12 +4177,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tapsoba</t>
+          <t>Raum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4143,7 +4191,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4152,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -4161,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -4181,21 +4229,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aleix Garcia</t>
+          <t>Ryerson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4204,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -4213,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -4233,21 +4281,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Tapsoba</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4256,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -4265,13 +4313,13 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4285,12 +4333,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>El Khannouss</t>
+          <t>Aleix Garcia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4299,28 +4347,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4337,12 +4385,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gruda</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4351,7 +4399,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4360,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -4389,12 +4437,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>El Khannouss</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4403,34 +4451,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4441,12 +4489,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pavlovic</t>
+          <t>Gruda</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4455,7 +4503,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -4464,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
@@ -4482,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4493,12 +4541,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Uzun</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4507,16 +4555,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I64" t="n">
         <v>2</v>
@@ -4525,16 +4573,16 @@
         <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4545,21 +4593,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Burkardt</t>
+          <t>Pavlovic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4568,25 +4616,25 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.67</v>
+        <v>2.7</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4597,33 +4645,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Demirovic</t>
+          <t>Uzun</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
@@ -4638,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4649,12 +4697,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Burkardt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4663,23 +4711,23 @@
         </is>
       </c>
       <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
         <v>4</v>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
@@ -4690,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4701,17 +4749,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Neuer</t>
+          <t>Demirovic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -4721,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>3.67</v>
+        <v>4.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -4739,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -4753,36 +4801,36 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Urbig</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4791,35 +4839,35 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Nusa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4828,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -4837,41 +4885,41 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Neuer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -4880,13 +4928,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4895,62 +4943,62 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Quansah</t>
+          <t>Urbig</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>6</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4961,12 +5009,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R. Koch</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4975,7 +5023,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4984,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4999,10 +5047,10 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -5013,21 +5061,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Avdullahu</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -5036,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -5051,10 +5099,10 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -5065,30 +5113,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Führich</t>
+          <t>Quansah</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -5097,16 +5145,16 @@
         <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5117,30 +5165,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kai. Sano</t>
+          <t>R. Koch</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -5149,13 +5197,13 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -5169,12 +5217,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Khedira</t>
+          <t>Avdullahu</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5183,22 +5231,22 @@
         </is>
       </c>
       <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
         <v>3</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3.67</v>
-      </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -5210,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5221,12 +5269,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>M. Eggestein</t>
+          <t>Führich</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5235,22 +5283,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>2.83</v>
+        <v>3.7</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -5273,12 +5321,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Kai. Sano</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5290,13 +5338,13 @@
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -5325,12 +5373,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Musiala</t>
+          <t>Khedira</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5339,7 +5387,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -5348,19 +5396,19 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -5377,12 +5425,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Petkov</t>
+          <t>M. Eggestein</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5391,7 +5439,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -5400,19 +5448,19 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -5429,12 +5477,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Prömel</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5443,7 +5491,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -5452,13 +5500,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -5481,21 +5529,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ebnoutalib</t>
+          <t>Musiala</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -5504,19 +5552,19 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -5533,21 +5581,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hlozek</t>
+          <t>Petkov</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -5556,19 +5604,19 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -5585,21 +5633,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Schick</t>
+          <t>Prömel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5608,25 +5656,25 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5637,12 +5685,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Undav</t>
+          <t>Ebnoutalib</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5660,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -5669,10 +5717,10 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5689,21 +5737,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Atubolu</t>
+          <t>Hlozek</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5712,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -5721,13 +5769,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -5736,74 +5784,74 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Schick</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Undav</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>STU</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -5816,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -5840,35 +5888,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kabak</t>
+          <t>Atubolu</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -5883,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -5897,12 +5945,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Schlotterbeck</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5911,16 +5959,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5935,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5949,12 +5997,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5966,13 +6014,13 @@
         <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -5981,16 +6029,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -6001,12 +6049,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tah</t>
+          <t>Kabak</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6021,10 +6069,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -6039,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -6053,21 +6101,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Beste</t>
+          <t>Schlotterbeck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -6076,13 +6124,13 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -6091,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -6105,21 +6153,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>El Aynaoui</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -6137,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -6157,30 +6205,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Tah</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -6195,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -6209,12 +6257,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Honorat</t>
+          <t>Beste</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gladbach</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6232,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -6241,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -6261,12 +6309,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>El Aynaoui</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6275,7 +6323,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -6284,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -6313,12 +6361,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nwaneri</t>
+          <t>Fabio Vieira</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6327,17 +6375,17 @@
         </is>
       </c>
       <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
         <v>4</v>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>3.5</v>
-      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -6345,10 +6393,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -6365,12 +6413,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Suzuki</t>
+          <t>Honorat</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6379,28 +6427,28 @@
         </is>
       </c>
       <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" t="n">
         <v>4</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -6417,12 +6465,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Veerman</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6431,22 +6479,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -6469,42 +6517,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Füllkrug</t>
+          <t>Nwaneri</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -6521,21 +6569,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Luis Diaz</t>
+          <t>Suzuki</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -6544,25 +6592,25 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6573,42 +6621,42 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mokwa</t>
+          <t>Veerman</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>STU</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -6625,12 +6673,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Saibari</t>
+          <t>Füllkrug</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bayern</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6639,7 +6687,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -6648,25 +6696,25 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6677,52 +6725,260 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>Luis Diaz</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>6</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Mokwa</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Saibari</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bayern</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>STU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nyland</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Wolfgang</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>Vandevoordt</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E106" t="n">
+      <c r="E110" t="n">
         <v>5</v>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
         <v>2.3</v>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
         <v>22</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N110" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N106"/>
+  <autoFilter ref="A1:N110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6818,10 +7074,10 @@
         <v>49.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="I2" t="n">
         <v>22.5</v>
@@ -6833,12 +7089,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Wolfgang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hallodries</t>
+          <t>Vickings</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -6851,10 +7107,10 @@
         <v>29.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>30.7</v>
+        <v>29.7</v>
       </c>
       <c r="I3" t="n">
         <v>2.7</v>
@@ -6866,31 +7122,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Great Licors</t>
+          <t>Hallodries</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>19.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>14.8</v>
+        <v>19.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-13.2</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="5">
@@ -6899,31 +7155,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wolfgang</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vickings</t>
+          <t>Great Licors</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="I5" t="n">
-        <v>-30</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="6">
@@ -6950,10 +7206,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I6" t="n">
         <v>-33</v>
@@ -6983,10 +7239,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I7" t="n">
         <v>-33</v>
@@ -7000,7 +7256,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 € je Manager und Spieltag (5 von 33 gewertet), Topf 198.0 €; 3.0 € je Spieltagssieg (geteilt anteilig); Meisterschaftstopf 99.0 €: 1. Platz 49.5 €, 2. Platz 29.7 €, 3. Platz 19.8 €; Auszahlung am Saisonende, Kassenwart Martin</t>
+          <t>1 € je Manager und Spieltag (6 von 33 gewertet), Topf 198.0 €; 3.0 € je Spieltagssieg (geteilt anteilig); Meisterschaftstopf 99.0 €: 1. Platz 49.5 €, 2. Platz 29.7 €, 3. Platz 19.8 €; Auszahlung am Saisonende, Kassenwart Martin</t>
         </is>
       </c>
     </row>
